--- a/data/credit_bond_all_2026-09-09.xlsx
+++ b/data/credit_bond_all_2026-09-09.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0400/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.6600/2.4000</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1911,7 +1911,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>2.02%~2.12%</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2048,7 +2052,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>102683569.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2127,7 +2135,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X9" s="3"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>2.07%~2.17%</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2251,7 +2263,9 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -2264,7 +2278,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102683574.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -2303,7 +2321,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1200/2.1100</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2343,7 +2361,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>2.11%~2.21%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2467,7 +2489,9 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -2480,7 +2504,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>102683575.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>15Y</t>
@@ -2519,7 +2547,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3200/2.3200</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2559,7 +2587,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>2.22%~2.32%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2687,7 +2719,9 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
@@ -2700,7 +2734,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>102683573.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -2739,7 +2777,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>1.7500/1.7200</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2779,7 +2817,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X12" s="3"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2916,7 +2958,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>042680309.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>0.88Y</t>
@@ -2955,7 +3001,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2995,7 +3041,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3132,7 +3182,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>102683568.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -3156,7 +3210,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26鄂交投债02(柜台)</t>
+          <t>26鄂交投债02</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -3171,7 +3225,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/1.7300</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3211,7 +3265,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3350,7 +3408,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>012682222.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -3429,7 +3491,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3566,7 +3632,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>042680310.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>0.49Y</t>
@@ -3605,7 +3675,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3645,7 +3715,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.86%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3774,7 +3848,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26核风电CP007(乡村振兴)</t>
+          <t>26核风电GN007(乡村振兴)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3782,7 +3856,11 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>132680094.IB</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>0.92Y</t>
@@ -3821,7 +3899,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -3861,7 +3939,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.46%~1.50%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3998,7 +4080,11 @@
           <t>09-10 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>102683577.IB</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -4077,7 +4163,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X18" s="3"/>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>2.08%~2.18%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4257,7 +4347,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9900/1.9300</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -4297,7 +4387,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X19" s="3"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>1.99%~2.09%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4477,7 +4571,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1400/2.1375</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4517,7 +4611,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X20" s="3"/>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>2.10%~2.20%</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4650,64 +4748,66 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26国信证券CP006</t>
+          <t>25浙能K2</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>09-09 17:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>072610178.IB</t>
+          <t>242734.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>30.0</v>
+        <v>6.0</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="4" t="n">
+        <v>2.15</v>
+      </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26国信证券CP003</t>
+          <t>24浙能源MTN001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>7.49Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.4800</t>
+          <t>1.9068</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9100/1.8800</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>浙江省能源集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 46.17</t>
+          <t>C- 20.21</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4717,7 +4817,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4727,19 +4827,19 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.95%~2.15%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4747,22 +4847,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z21" s="3"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
-        </is>
-      </c>
-      <c r="AB21" s="3"/>
+          <t>浙江省-杭州市</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后，拟将全部用于偿还到期的中期票据本金【22 浙能源 MTN001】</t>
+        </is>
+      </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>财通证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4772,12 +4880,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司2026年度第六期短期融资券</t>
+          <t>浙江省能源集团有限公司2025年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4787,53 +4895,57 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-03-12</t>
-        </is>
-      </c>
-      <c r="AK21" s="3"/>
+          <t>2035-04-14</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4957,7 +5069,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="X22" s="3"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5137,7 +5253,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8500</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5177,7 +5293,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>1.99%~2.09%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5585,7 +5705,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>1.7250/1.7000</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -5625,7 +5745,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X25" s="3"/>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5805,7 +5929,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -5845,7 +5969,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6029,7 +6157,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6300/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6069,7 +6197,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X27" s="3"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6289,7 +6421,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X28" s="3"/>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6505,7 +6641,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X29" s="3"/>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>1.94%~2.04%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6685,7 +6825,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.8100/--</t>
+          <t>1.7800/1.7600</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -6725,7 +6865,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X30" s="3"/>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>2.04%~2.14%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6905,7 +7049,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2600/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -6945,7 +7089,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X31" s="3"/>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>2.50%~2.60%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -7125,7 +7273,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9100/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -7165,7 +7313,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X32" s="3"/>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.91%~2.01%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7385,7 +7537,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X33" s="3"/>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -7569,7 +7725,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9100/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -7609,7 +7765,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X34" s="3"/>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7785,7 +7945,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/3.5000</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -7825,7 +7985,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X35" s="3"/>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>2.88%~2.98%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -8001,7 +8165,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/3.5000</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -8041,7 +8205,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X36" s="3"/>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>2.56%~2.66%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -8170,70 +8338,68 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26舟山海投MTN001</t>
+          <t>26光证G6</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>102683531.IB</t>
+          <t>246032.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4.93Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>50.0</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 2.35</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26舟投01</t>
+          <t>26光证G5</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>4.83Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.8448</t>
+          <t>1.7257</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7750/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>舟山海洋投资集团有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>D 3.33</t>
+          <t>B 50.41</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8243,7 +8409,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-09 14:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8260,14 +8426,10 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t>1.75%~1.85%</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X37" s="3"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8276,38 +8438,38 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>浙江省-舟山市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据注册规模为 20.00 亿元，本期发行金额 10.00 亿元，募集资金拟全部用于偿还发行人子公司债务融资工具到期本金。 [23 舟山海洋MTN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金、补充流动资金；本期债券募集资金30亿元拟用于偿还到期公司债券本金；本期债券募集资金20亿元用于补充公司日常经营所需流动资金[26光证S1]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,宁波银行股份有限公司</t>
+          <t>兴业证券股份有限公司,招商证券股份有限公司,东方证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>舟山海洋投资集团有限公司2026年度第一期中期票据</t>
+          <t>光大证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8317,18 +8479,22 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2031-08-16</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t/>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
@@ -8338,32 +8504,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>渔业</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8388,7 +8554,7 @@
       </c>
       <c r="AY37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AZ37" s="3"/>
@@ -8396,64 +8562,66 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26武汉农商绿色债</t>
+          <t>26国信证券CP006</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
-        </is>
-      </c>
-      <c r="C38" s="3"/>
+          <t>09-09 17:00</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>072610178.IB</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>6.0</v>
+        <v>30.0</v>
       </c>
       <c r="F38" s="3"/>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>1.30 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25武汉农商科创债(柜台)</t>
+          <t>26国信证券CP003</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>4.01Y</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6184</t>
+          <t>1.4800</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>武汉农村商业银行股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>B- 46.17</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8463,7 +8631,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-09 10:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8473,19 +8641,19 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8493,30 +8661,22 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
-        </is>
-      </c>
-      <c r="AB38" s="3" t="inlineStr">
-        <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
-        </is>
-      </c>
+          <t>广东省-深圳市</t>
+        </is>
+      </c>
+      <c r="AB38" s="3"/>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,长江证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8531,7 +8691,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>武汉农村商业银行股份有限公司2026年绿色金融债券</t>
+          <t>国信证券股份有限公司2026年度第六期短期融资券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8541,23 +8701,23 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO38" s="3" t="inlineStr">
@@ -8567,27 +8727,27 @@
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8620,17 +8780,17 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26青信11</t>
+          <t>26舟山海投MTN001</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>246028.SH</t>
+          <t>102683531.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -8639,34 +8799,36 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.35 ~ 2.35</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26青岛国信MTN008A</t>
+          <t>26舟投01</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.8949</t>
+          <t>1.8448</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -8676,12 +8838,12 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>青岛国信发展(集团)有限责任公司</t>
+          <t>舟山海洋投资集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.54</t>
+          <t>D 3.33</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8691,7 +8853,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 14:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8708,10 +8870,14 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X39" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8720,23 +8886,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>浙江省-舟山市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金[21青纾01]</t>
+          <t>发行人本次中期票据注册规模为 20.00 亿元，本期发行金额 10.00 亿元，募集资金拟全部用于偿还发行人子公司债务融资工具到期本金。 [23 舟山海洋MTN001]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -8746,12 +8912,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第六期)(品种一)</t>
+          <t>舟山海洋投资集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8767,54 +8933,54 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>渔业</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO39" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ39" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR39" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8832,7 +8998,7 @@
       </c>
       <c r="AY39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AZ39" s="3"/>
@@ -8840,7 +9006,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26青信12</t>
+          <t>26武汉农商绿色债</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8848,45 +9014,41 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>246029.SH</t>
-        </is>
-      </c>
+      <c r="C40" s="3"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3.5</v>
+        <v>6.0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.30 ~ 2.00</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26青岛国信MTN008B</t>
+          <t>25武汉农商科创债(柜台)</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>9.96Y</t>
+          <t>4.01Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2.3856</t>
+          <t>1.6184</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -8896,12 +9058,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>青岛国信发展(集团)有限责任公司</t>
+          <t>武汉农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.54</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8911,7 +9073,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 10:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -8928,35 +9090,43 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X40" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z40" s="3"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金[21青纾01]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,长江证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -8966,12 +9136,12 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第六期)(品种二)</t>
+          <t>武汉农村商业银行股份有限公司2026年绿色金融债券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -8981,7 +9151,7 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2036-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
@@ -8992,7 +9162,7 @@
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN40" s="3" t="inlineStr">
@@ -9002,32 +9172,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9060,64 +9230,68 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26上海农商01</t>
+          <t>26青信11</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:30</t>
-        </is>
-      </c>
-      <c r="C41" s="3"/>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>246028.SH</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>30.0</v>
+        <v>3.5</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>25上海农商01(柜台)</t>
+          <t>26青岛国信MTN008A</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>1.83Y</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.5136</t>
+          <t>1.8949</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8900/1.8600</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>上海农村商业银行股份有限公司</t>
+          <t>青岛国信发展(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C+ 30.54</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9127,7 +9301,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9144,12 +9318,12 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9160,23 +9334,23 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金[21青纾01]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国银行股份有限公司,中信银行股份有限公司,上海银行股份有限公司,申万宏源证券有限公司</t>
+          <t>中信证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9186,12 +9360,12 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>上海农村商业银行股份有限公司2026年金融债券(第一期)</t>
+          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第六期)(品种一)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9201,7 +9375,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9212,7 +9386,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
@@ -9222,32 +9396,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9280,7 +9454,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26昆北01</t>
+          <t>26青信12</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9290,58 +9464,58 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283863.SH</t>
+          <t>246029.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>10.0</v>
+        <v>3.5</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26沪苏01</t>
+          <t>26青岛国信MTN008B</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>4.69Y</t>
+          <t>9.96Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.9247</t>
+          <t>2.3856</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.4000/2.3700</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>昆山北部新城集团有限公司</t>
+          <t>青岛国信发展(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>C+ 30.54</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9351,7 +9525,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9368,29 +9542,33 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X42" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>2.31%~2.41%</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还公司债券本金[24昆北01]</t>
+          <t>本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金[21青纾01]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中信证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
@@ -9411,17 +9589,17 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>昆山北部新城集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第六期)(品种二)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2036-09-11</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
@@ -9432,7 +9610,7 @@
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
@@ -9442,32 +9620,32 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>7.5*无效</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>环保工程及服务</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9500,18 +9678,18 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26东航SCP003</t>
+          <t>26上海农商01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 16:30</t>
         </is>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -9520,29 +9698,29 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.51</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>25东航MTN001</t>
+          <t>25上海农商01(柜台)</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>1.83Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.5879</t>
+          <t>1.5136</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -9552,12 +9730,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空集团有限公司</t>
+          <t>上海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.52</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9577,17 +9755,21 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X43" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.58%~1.68%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -9601,23 +9783,23 @@
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为30亿元，所募集资金拟用于本级和下属企业归还存量债务及补充营运资金。</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,杭州银行股份有限公司,南京银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国银行股份有限公司,中信银行股份有限公司,上海银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
@@ -9627,7 +9809,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空集团有限公司2026年度第三期超短期融资券</t>
+          <t>上海农村商业银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -9637,53 +9819,53 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2027-04-08</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -9716,7 +9898,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26京能租赁CP002</t>
+          <t>26昆北01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9724,41 +9906,45 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C44" s="3"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>283863.SH</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>0.9Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.57</t>
+          <t>1.80 ~ 3.00</t>
         </is>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26京能租赁CP001</t>
+          <t>26沪苏01</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>219D</t>
+          <t>4.69Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.5290</t>
+          <t>1.9247</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -9768,12 +9954,12 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>北京京能融资租赁有限公司</t>
+          <t>昆山北部新城集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>D- 3.00</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -9783,7 +9969,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -9793,42 +9979,46 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X44" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本次短期融资券拟募集资金5亿元,拟全部用于偿还发行人存量有息债务。</t>
+          <t>本期债券募集资金拟全部用于偿还公司债券本金[24昆北01]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -9838,68 +10028,68 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>北京京能融资租赁有限公司2026年度第二期短期融资券</t>
+          <t>昆山北部新城集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2027-08-06</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5*无效</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>环保工程及服务</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -9932,7 +10122,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26核风电GN008</t>
+          <t>26东航SCP003</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -9940,56 +10130,60 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C45" s="3"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>012682224.IB</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>0.92Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>15.0</v>
+        <v>30.0</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.33 ~ 1.53</t>
+          <t>1.30 ~ 1.51</t>
         </is>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>24风电GVK1</t>
+          <t>25东航MTN001</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>317D</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.4977</t>
+          <t>1.5879</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6175/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>中广核风电有限公司</t>
+          <t>中国东方航空集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 17.02</t>
+          <t>C+ 31.52</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -9999,7 +10193,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-09 14:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10019,7 +10213,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X45" s="3"/>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10028,28 +10226,28 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期绿色短期融资券15亿元募集资金拟用于置换发行人三个月内在帆石一期、贵州龙里坪子风电场项目、大嘎吉20万千瓦光伏3个绿色项目建设运营的自有资金支出</t>
+          <t>本期超短期融资券发行金额为30亿元，所募集资金拟用于本级和下属企业归还存量债务及补充营运资金。</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
+          <t>中信银行股份有限公司,杭州银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10059,7 +10257,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>中广核风电有限公司2026年度第八期绿色短期融资券</t>
+          <t>中国东方航空集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10069,7 +10267,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2027-08-10</t>
+          <t>2027-04-08</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10095,27 +10293,27 @@
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10148,7 +10346,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26长沙水业MTN003</t>
+          <t>26京能租赁CP002</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10156,10 +10354,14 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C46" s="3"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>042680311.IB</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.9Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -10168,44 +10370,44 @@
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.37 ~ 1.57</t>
         </is>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26长沙水业MTN001</t>
+          <t>26京能租赁CP001</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+N</t>
+          <t>219D</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.7717</t>
+          <t>1.5290</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>长沙水业集团有限公司</t>
+          <t>北京京能融资租赁有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 22.98</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10235,32 +10437,36 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X46" s="3"/>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.60%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟募集资金5亿元,所募集资金拟用于偿还发行人存量债务融资工具[23长沙水业MTN004]</t>
+          <t>本次短期融资券拟募集资金5亿元,拟全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,财信证券股份有限公司</t>
+          <t>北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
@@ -10275,7 +10481,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>长沙水业集团有限公司2026年度第三期中期票据</t>
+          <t>北京京能融资租赁有限公司2026年度第二期短期融资券</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10285,7 +10491,7 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2027-08-06</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
@@ -10306,7 +10512,7 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
@@ -10316,22 +10522,22 @@
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10346,7 +10552,7 @@
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10364,64 +10570,68 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26粤铁建MTN005</t>
+          <t>26核风电GN008</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
-        </is>
-      </c>
-      <c r="C47" s="3"/>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>132680095.IB</t>
+        </is>
+      </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.92Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.33 ~ 1.53</t>
         </is>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26粤铁建MTN004</t>
+          <t>24风电GVK1</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>317D</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.6862</t>
+          <t>1.4977</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>广东省铁路建设投资集团有限公司</t>
+          <t>中广核风电有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>B- 49.09</t>
+          <t>C- 17.02</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10431,7 +10641,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 14:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10441,7 +10651,7 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U47" s="3"/>
@@ -10451,7 +10661,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X47" s="3"/>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>1.46%~1.50%</t>
+        </is>
+      </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10460,24 +10674,28 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>广东省</t>
-        </is>
-      </c>
-      <c r="AB47" s="3"/>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>本期绿色短期融资券15亿元募集资金拟用于置换发行人三个月内在帆石一期、贵州龙里坪子风电场项目、大嘎吉20万千瓦光伏3个绿色项目建设运营的自有资金支出</t>
+        </is>
+      </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG47" s="3" t="inlineStr">
@@ -10487,7 +10705,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>广东省铁路建设投资集团有限公司2026年度第五期中期票据</t>
+          <t>中广核风电有限公司2026年度第八期绿色短期融资券</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10497,13 +10715,13 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2027-08-10</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM47" s="3" t="inlineStr">
@@ -10513,37 +10731,37 @@
       </c>
       <c r="AN47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10568,7 +10786,7 @@
       </c>
       <c r="AY47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AZ47" s="3"/>
@@ -10576,7 +10794,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26鄂联投MTN001</t>
+          <t>26长沙水业MTN003</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -10584,14 +10802,18 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C48" s="3"/>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>102683570.IB</t>
+        </is>
+      </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
@@ -10608,32 +10830,32 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26联投Y4</t>
+          <t>26长沙水业MTN001</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.80Y+N</t>
+          <t>2.88Y+N</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.8065</t>
+          <t>1.7717</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>1.8400/--</t>
+          <t>1.8100/1.7200</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>湖北省联合发展投资集团有限公司</t>
+          <t>长沙水业集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.00</t>
+          <t>C- 22.98</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -10643,7 +10865,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -10660,29 +10882,33 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X48" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为7亿元,募集资金拟全部用于偿还发行人非金融企业债务融资工具本金[23鄂联投MTN004]</t>
+          <t>本期中期票据拟募集资金5亿元,所募集资金拟用于偿还发行人存量债务融资工具[23长沙水业MTN004]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,浙商银行股份有限公司</t>
+          <t>招商银行股份有限公司,财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
@@ -10703,7 +10929,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>湖北省联合发展投资集团有限公司2026年度第一期中期票据</t>
+          <t>长沙水业集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -10739,27 +10965,27 @@
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -10787,71 +11013,73 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ48" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ48" s="3"/>
     </row>
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26三峡文旅SCP003</t>
+          <t>26粤铁建MTN005</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
-        </is>
-      </c>
-      <c r="C49" s="3"/>
+          <t>09-10 18:00</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>102683578.IB</t>
+        </is>
+      </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26三峡文旅SCP002</t>
+          <t>26粤铁建MTN004</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>251D</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.7034</t>
+          <t>1.6862</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6850/1.6700</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>湖北三峡文化旅游集团有限公司</t>
+          <t>广东省铁路建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>B- 35.77</t>
+          <t>B- 49.09</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -10861,7 +11089,7 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>09-09 11:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -10871,42 +11099,42 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X49" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
-        </is>
-      </c>
-      <c r="AB49" s="3" t="inlineStr">
-        <is>
-          <t>本次超短期融资券注册金额为20亿元,基础发行规模0亿元,发行金额上限为5亿元,募集资金拟用于偿还有息负债</t>
-        </is>
-      </c>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="AB49" s="3"/>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,兴业银行股份有限公司</t>
+          <t>中国银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
@@ -10921,7 +11149,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>湖北三峡文化旅游集团有限公司2026年度第三期超短期融资券</t>
+          <t>广东省铁路建设投资集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -10931,88 +11159,86 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN49" s="3" t="inlineStr">
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY49" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AO49" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ49" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR49" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW49" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX49" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AZ49" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ49" s="3"/>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26中远海运SCP004</t>
+          <t>26鄂联投MTN001</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -11020,56 +11246,60 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C50" s="3"/>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>102683571.IB</t>
+        </is>
+      </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>30.0</v>
+        <v>7.0</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.46</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>18远海05</t>
+          <t>26联投Y4</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2.16Y</t>
+          <t>2.80Y+N</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.5747</t>
+          <t>1.8065</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/--</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>中国远洋海运集团有限公司</t>
+          <t>湖北省联合发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.80</t>
+          <t>C+ 33.00</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11079,7 +11309,7 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -11096,10 +11326,14 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X50" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11108,28 +11342,28 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本次募集资金30亿元用于偿还发行人本部及合并报表范围内子公司的有息债务及用于生产经营活动。</t>
+          <t>本期中期票据发行金额为7亿元,募集资金拟全部用于偿还发行人非金融企业债务融资工具本金[23鄂联投MTN004]</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr">
@@ -11139,7 +11373,7 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>中国远洋海运集团有限公司2026年度第四期超短期融资券</t>
+          <t>湖北省联合发展投资集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
@@ -11149,7 +11383,7 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK50" s="3"/>
@@ -11170,32 +11404,32 @@
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11210,7 +11444,7 @@
       </c>
       <c r="AW50" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX50" s="3" t="inlineStr">
@@ -11223,12 +11457,14 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ50" s="3"/>
+      <c r="AZ50" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26南昌轨交GN005</t>
+          <t>26三峡文旅SCP003</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11236,41 +11472,45 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C51" s="3"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>012682225.IB</t>
+        </is>
+      </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.18</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>26南昌轨交MTN004(绿色)</t>
+          <t>26三峡文旅SCP002</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>251D</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.7778</t>
+          <t>1.7034</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -11280,12 +11520,12 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>南昌轨道交通集团有限公司</t>
+          <t>湖北三峡文化旅游集团有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C 28.63</t>
+          <t>B- 35.77</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11295,7 +11535,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 11:00</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -11312,35 +11552,39 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X51" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.71%</t>
+        </is>
+      </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币10亿元,募集资金用于偿还有息债务[21南昌轨交MTN001]</t>
+          <t>本次超短期融资券注册金额为20亿元,基础发行规模0亿元,发行金额上限为5亿元,募集资金拟用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
+          <t>兴业证券股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
@@ -11355,7 +11599,7 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>南昌轨道交通集团有限公司2026年度第五期绿色中期票据</t>
+          <t>湖北三峡文化旅游集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -11365,7 +11609,7 @@
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2036-09-10</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK51" s="3"/>
@@ -11401,17 +11645,17 @@
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -11439,12 +11683,14 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ51" s="3"/>
+      <c r="AZ51" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26青岛华通MTN002(并购)</t>
+          <t>26中远海运SCP004</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -11452,56 +11698,60 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C52" s="3"/>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>012682223.IB</t>
+        </is>
+      </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>4.0</v>
+        <v>30.0</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.20 ~ 1.46</t>
         </is>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26青岛华通MTN001</t>
+          <t>18远海05</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2.75Y+2.00Y</t>
+          <t>2.16Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.7574</t>
+          <t>1.5747</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>青岛华通国有资本投资运营集团有限公司</t>
+          <t>中国远洋海运集团有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>B- 47.27</t>
+          <t>C+ 30.80</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -11528,10 +11778,14 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X52" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11540,28 +11794,28 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟发行金额4亿元,募集资金全部用于支付并购价款,具体用于全资子公司海信集团有限公司支付定增款项,实现海信集团对海信集团控股股份有限公司的持股比例增加。</t>
+          <t>发行人拟将本次募集资金30亿元用于偿还发行人本部及合并报表范围内子公司的有息债务及用于生产经营活动。</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>青岛银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG52" s="3" t="inlineStr">
@@ -11571,7 +11825,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>青岛华通国有资本投资运营集团有限公司2026年度第二期中期票据(并购)</t>
+          <t>中国远洋海运集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -11581,7 +11835,7 @@
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="AK52" s="3"/>
@@ -11607,27 +11861,27 @@
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -11660,7 +11914,7 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26中兵投资SCP002</t>
+          <t>26南昌轨交MTN005(绿色)(取消发行)</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -11668,10 +11922,14 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C53" s="3"/>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>DY102683576.IB</t>
+        </is>
+      </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -11680,44 +11938,44 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.33 ~ 1.53</t>
+          <t>2.00 ~ 2.18</t>
         </is>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>24中兵01</t>
+          <t>26南昌轨交MTN004(绿色)</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>254D+2.00Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.5482</t>
+          <t>1.7778</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>中兵投资管理有限责任公司</t>
+          <t>南昌轨道交通集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 17.85</t>
+          <t>C 28.63</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -11727,7 +11985,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>09-09 11:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -11744,40 +12002,44 @@
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X53" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>2.21%~2.31%</t>
+        </is>
+      </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元,所募集资金10亿元拟用于偿还发行人到期债券23中兵投资MTN001本金[23中兵投资MTN001]</t>
+          <t>本期中期票据发行金额为人民币10亿元,募集资金用于偿还有息债务[21南昌轨交MTN001]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG53" s="3" t="inlineStr">
@@ -11787,7 +12049,7 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>中兵投资管理有限责任公司2026年度第二期超短期融资券</t>
+          <t>南昌轨道交通集团有限公司2026年度第五期绿色中期票据(取消发行)</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -11797,7 +12059,7 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2036-09-10</t>
         </is>
       </c>
       <c r="AK53" s="3"/>
@@ -11818,32 +12080,32 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
@@ -11871,14 +12133,12 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ53" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ53" s="3"/>
     </row>
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26南京公路SCP002</t>
+          <t>26青岛华通MTN002(并购)</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -11886,56 +12146,60 @@
           <t>09-09 18:00</t>
         </is>
       </c>
-      <c r="C54" s="3"/>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>102683572.IB</t>
+        </is>
+      </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26南京公路SCP001</t>
+          <t>26青岛华通MTN001</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>241D</t>
+          <t>2.75Y+2.00Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.5252</t>
+          <t>1.7574</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>1.5800/--</t>
+          <t>1.7650/1.7000</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>青岛华通国有资本投资运营集团有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C- 23.23</t>
+          <t>B- 47.27</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -11962,39 +12226,39 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X54" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及下属子公司有息债务。</t>
+          <t>本期债券拟发行金额4亿元,募集资金全部用于支付并购价款,具体用于全资子公司海信集团有限公司支付定增款项,实现海信集团对海信集团控股股份有限公司的持股比例增加。</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD54" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>青岛银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD54" s="3"/>
       <c r="AE54" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF54" s="3" t="inlineStr">
@@ -12009,7 +12273,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第二期超短期融资券</t>
+          <t>青岛华通国有资本投资运营集团有限公司2026年度第二期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12019,7 +12283,7 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK54" s="3"/>
@@ -12040,32 +12304,32 @@
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
@@ -12075,7 +12339,7 @@
       </c>
       <c r="AV54" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW54" s="3" t="inlineStr">
@@ -12098,7 +12362,7 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26桂铁07</t>
+          <t>26中兵投资SCP002</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12108,12 +12372,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>524938.SZ</t>
+          <t>012682226.IB</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
@@ -12122,44 +12386,44 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.33 ~ 1.53</t>
         </is>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26桂铁05</t>
+          <t>24中兵01</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+2.00Y</t>
+          <t>254D+2.00Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.7447</t>
+          <t>1.5482</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5300</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司</t>
+          <t>中兵投资管理有限责任公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>B- 45.02</t>
+          <t>C- 17.85</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12169,7 +12433,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 11:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12179,57 +12443,61 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X55" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.56%</t>
+        </is>
+      </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[21桂铁03]</t>
+          <t>本期超短期融资券发行金额为10亿元,所募集资金10亿元拟用于偿还发行人到期债券23中兵投资MTN001本金[23中兵投资MTN001]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,平安证券股份有限公司,兴业证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF55" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG55" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>中兵投资管理有限责任公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12239,60 +12507,60 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO55" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ55" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR55" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AS55" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU55" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-11</t>
-        </is>
-      </c>
       <c r="AV55" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -12300,7 +12568,7 @@
       </c>
       <c r="AW55" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX55" s="3" t="inlineStr">
@@ -12313,12 +12581,14 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ55" s="3"/>
+      <c r="AZ55" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>G26浙租1</t>
+          <t>26南京公路SCP002</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -12328,58 +12598,58 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>246016.SH</t>
+          <t>012682221.IB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>24浙商租赁MTN001</t>
+          <t>26南京公路SCP001</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>253D</t>
+          <t>241D</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.5501</t>
+          <t>1.5252</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/1.4900</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>浙江浙商融资租赁有限公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.83</t>
+          <t>C- 23.23</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -12389,7 +12659,7 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -12399,42 +12669,50 @@
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X56" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.56%</t>
+        </is>
+      </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期发行规模不超过10亿元(含10亿元),募集资金拟用于置换本期债券发行前12个月内发行人用于绿色项目租赁款投放的自有资金支出。</t>
+          <t>本期超短期融资券发行金额3亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及下属子公司有息债务。</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD56" s="3"/>
+          <t>中信银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr">
+        <is>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+        </is>
+      </c>
       <c r="AE56" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF56" s="3" t="inlineStr">
@@ -12444,12 +12722,12 @@
       </c>
       <c r="AG56" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>浙江浙商融资租赁有限公司2026年面向专业投资者公开发行绿色公司债券(第一期)</t>
+          <t>南京公路发展(集团)有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -12459,63 +12737,63 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM56" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO56" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ56" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR56" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS56" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV56" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW56" s="3" t="inlineStr">
@@ -12533,12 +12811,14 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ56" s="3"/>
+      <c r="AZ56" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26中泰05</t>
+          <t>26桂铁07</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -12548,58 +12828,58 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>246007.SH</t>
+          <t>524938.SZ</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26中泰04</t>
+          <t>26桂铁05</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>2.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.6705</t>
+          <t>1.7447</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7300</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>广西铁路投资集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>B- 45.26</t>
+          <t>B- 45.02</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -12626,10 +12906,14 @@
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X57" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -12638,23 +12922,23 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过15亿元(含)用于置换公司偿还到期公司债券本金的自有资金;不超过15亿元(含)用于补充公司流动资金,满足公司业务运营需要。[21中泰03]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[21桂铁03]</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>东方证券股份有限公司,平安证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
@@ -12664,12 +12948,12 @@
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
+          <t>广西铁路投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -12679,7 +12963,7 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
@@ -12700,37 +12984,37 @@
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
@@ -12740,7 +13024,7 @@
       </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX57" s="3" t="inlineStr">
@@ -12758,7 +13042,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26内投01</t>
+          <t>G26浙租1</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -12768,58 +13052,58 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>283914.SH</t>
+          <t>246016.SH</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.1</v>
+        <v>10.0</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26内江投控PPN001</t>
+          <t>24浙商租赁MTN001</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>4.59Y+5.00Y</t>
+          <t>253D</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>2.2273</t>
+          <t>1.5501</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/1.5300</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>内江投资控股集团有限公司</t>
+          <t>浙江浙商融资租赁有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.64</t>
+          <t>D+ 7.83</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -12839,17 +13123,21 @@
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X58" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -12858,17 +13146,17 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>四川省-内江市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还23内江01公司债券本金[23内江01]</t>
+          <t>本期发行规模不超过10亿元(含10亿元),募集资金拟用于置换本期债券发行前12个月内发行人用于绿色项目租赁款投放的自有资金支出。</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>华源证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
@@ -12889,17 +13177,17 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>内江投资控股集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>浙江浙商融资租赁有限公司2026年面向专业投资者公开发行绿色公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2036-09-10</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -12915,42 +13203,42 @@
       </c>
       <c r="AN58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AV58" s="3" t="inlineStr">
@@ -12960,7 +13248,7 @@
       </c>
       <c r="AW58" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX58" s="3" t="inlineStr">
@@ -12978,7 +13266,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26沿海05</t>
+          <t>26中泰05</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -12988,58 +13276,58 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>283934.SH</t>
+          <t>246007.SH</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26沿海04</t>
+          <t>26中泰04</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.93Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.8960</t>
+          <t>1.6705</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/1.6600</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>南通沿海开发集团有限公司</t>
+          <t>中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>B- 44.25</t>
+          <t>B- 45.26</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13049,7 +13337,7 @@
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -13066,10 +13354,14 @@
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X59" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13078,23 +13370,23 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司将到期的公司债券本金[23沿海04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过15亿元(含)用于置换公司偿还到期公司债券本金的自有资金;不超过15亿元(含)用于补充公司流动资金,满足公司业务运营需要。[21中泰03]</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,东方证券股份有限公司,东吴证券股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
@@ -13109,17 +13401,17 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>南通沿海开发集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
@@ -13140,32 +13432,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>其他休闲服务</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13198,7 +13490,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26驻产02</t>
+          <t>26内投01</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13208,58 +13500,58 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>283874.SH</t>
+          <t>283914.SH</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>3.24</v>
+        <v>5.1</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26驻产01</t>
+          <t>26内江投控PPN001</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>4.54Y</t>
+          <t>4.59Y+5.00Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2.0882</t>
+          <t>2.2273</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2700/2.1500</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>驻马店市产业投资集团有限公司</t>
+          <t>内江投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>B- 37.44</t>
+          <t>C+ 33.64</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13269,7 +13561,7 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -13279,36 +13571,40 @@
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X60" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>河南省-驻马店市</t>
+          <t>四川省-内江市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本次债券发行金额为不超过人民币3.24亿元(含3.24亿元),扣除发行费用后,计划全部用于偿还到期的公司债券本金。[23驻产06]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还23内江01公司债券本金[23内江01]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,光大证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>华源证券股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
@@ -13329,7 +13625,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>驻马店市产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>内江投资控股集团有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -13339,7 +13635,7 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2036-09-10</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
@@ -13355,22 +13651,34 @@
       </c>
       <c r="AN60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ60" s="3"/>
-      <c r="AR60" s="3"/>
-      <c r="AS60" s="3"/>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -13378,7 +13686,7 @@
       </c>
       <c r="AU60" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AV60" s="3" t="inlineStr">
@@ -13388,7 +13696,7 @@
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr">
@@ -13406,7 +13714,7 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26冀交Y4</t>
+          <t>26沿海05</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -13416,58 +13724,58 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>283916.SH</t>
+          <t>283934.SH</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>24冀交03</t>
+          <t>26沿海04</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.7554</t>
+          <t>1.8960</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9500/--</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>河北交通投资集团有限公司</t>
+          <t>南通沿海开发集团有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C- 23.39</t>
+          <t>B- 44.25</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -13477,7 +13785,7 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -13494,10 +13802,14 @@
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X61" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>1.87%~1.97%</t>
+        </is>
+      </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13506,17 +13818,17 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟使用8亿元用于偿还公司债券本金[23冀交05]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司将到期的公司债券本金[23沿海04]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,财达证券股份有限公司</t>
+          <t>中信证券股份有限公司,东方证券股份有限公司,东吴证券股份有限公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
@@ -13537,7 +13849,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>河北交通投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
+          <t>南通沿海开发集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -13547,7 +13859,7 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK61" s="3"/>
@@ -13568,12 +13880,12 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
@@ -13583,17 +13895,17 @@
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>其他休闲服务</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -13608,12 +13920,12 @@
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX61" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY61" s="3" t="inlineStr">
@@ -13626,7 +13938,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26武金05</t>
+          <t>26驻产02</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -13636,16 +13948,16 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>283578.SH</t>
+          <t>283874.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>6.0</v>
+        <v>3.24</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="inlineStr">
@@ -13657,37 +13969,37 @@
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26武金04</t>
+          <t>26驻产01</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>4.81Y</t>
+          <t>4.54Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>2.1647</t>
+          <t>2.0882</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.1000</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>武汉金融控股(集团)有限公司</t>
+          <t>驻马店市产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.34</t>
+          <t>B- 37.44</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -13697,7 +14009,7 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
@@ -13707,36 +14019,40 @@
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X62" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>2.10%~2.20%</t>
+        </is>
+      </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>河南省-驻马店市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后拟用于对子公司武汉阳逻开发有限公司增资</t>
+          <t>本次债券发行金额为不超过人民币3.24亿元(含3.24亿元),扣除发行费用后,计划全部用于偿还到期的公司债券本金。[23驻产06]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,长城证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,华源证券股份有限公司,兴业证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,光大证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
@@ -13757,95 +14073,1639 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
+          <t>驻马店市产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI62" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ62" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-11</t>
+        </is>
+      </c>
+      <c r="AK62" s="3"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ62" s="3"/>
+      <c r="AR62" s="3"/>
+      <c r="AS62" s="3"/>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX62" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AZ62" s="3"/>
+    </row>
+    <row r="63" customHeight="true" ht="18.0">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>26冀交Y4</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>283916.SH</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>24冀交Y3</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>2.85Y+N</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>1.8045</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>河北交通投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>C- 23.39</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>09-09 15:00</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>河北省</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金拟使用8亿元用于偿还公司债券本金[23冀交05]</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,财达证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD63" s="3"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr">
+        <is>
+          <t>河北交通投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-11</t>
+        </is>
+      </c>
+      <c r="AK63" s="3"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ63" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX63" s="3" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AY63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AZ63" s="3"/>
+    </row>
+    <row r="64" customHeight="true" ht="18.0">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>26武金05</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>283578.SH</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>5+5</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>26武金04</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>4.81Y</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>2.1647</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>武汉金融控股(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>C+ 32.34</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>09-09 15:00</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>2.12%~2.22%</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>湖北省-武汉市</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后拟用于对子公司武汉阳逻开发有限公司增资</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>长江证券股份有限公司,长城证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,华源证券股份有限公司,兴业证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD64" s="3"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr">
+        <is>
           <t>武汉金融控股(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
-      <c r="AI62" s="3" t="inlineStr">
+      <c r="AI64" s="3" t="inlineStr">
         <is>
           <t>私募</t>
         </is>
       </c>
-      <c r="AJ62" s="3" t="inlineStr">
+      <c r="AJ64" s="3" t="inlineStr">
         <is>
           <t>2036-09-14</t>
         </is>
       </c>
-      <c r="AK62" s="3" t="inlineStr">
+      <c r="AK64" s="3" t="inlineStr">
         <is>
           <t>休1</t>
         </is>
       </c>
-      <c r="AL62" s="3" t="inlineStr">
+      <c r="AL64" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AM62" s="3" t="inlineStr">
+      <c r="AM64" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
+      <c r="AN64" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AO62" s="3" t="inlineStr">
+      <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>金融</t>
         </is>
       </c>
-      <c r="AP62" s="3" t="inlineStr">
+      <c r="AP64" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AQ62" s="3" t="inlineStr">
+      <c r="AQ64" s="3" t="inlineStr">
         <is>
           <t>非银</t>
         </is>
       </c>
-      <c r="AR62" s="3" t="inlineStr">
+      <c r="AR64" s="3" t="inlineStr">
         <is>
           <t>金融控股</t>
         </is>
       </c>
-      <c r="AS62" s="3" t="inlineStr">
+      <c r="AS64" s="3" t="inlineStr">
         <is>
           <t>金融控股</t>
         </is>
       </c>
-      <c r="AT62" s="3" t="inlineStr">
+      <c r="AT64" s="3" t="inlineStr">
         <is>
           <t>多元金融</t>
         </is>
       </c>
-      <c r="AU62" s="3" t="inlineStr">
+      <c r="AU64" s="3" t="inlineStr">
         <is>
           <t>2031-09-14</t>
         </is>
       </c>
-      <c r="AV62" s="3" t="inlineStr">
+      <c r="AV64" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AW62" s="3" t="inlineStr">
+      <c r="AW64" s="3" t="inlineStr">
         <is>
           <t>含权</t>
         </is>
       </c>
-      <c r="AX62" s="3" t="inlineStr">
+      <c r="AX64" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AY62" s="3" t="inlineStr">
+      <c r="AY64" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ62" s="3"/>
+      <c r="AZ64" s="3"/>
+    </row>
+    <row r="65" customHeight="true" ht="18.0">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>26临交02</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>283893.SH</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>26临平交通PPN004</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>2.99Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>1.7378</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>1.7499/1.7100</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>杭州临平交通集团有限公司</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>B- 46.22</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>09-09 16:00</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>浙江省-杭州市</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行总额不超过人民币5.4亿元(含5.4亿元)，扣除发行费用后，全部用于偿还到期公司债券本金[23临交03]</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD65" s="3"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr">
+        <is>
+          <t>杭州临平交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-11</t>
+        </is>
+      </c>
+      <c r="AK65" s="3"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ65" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-11</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX65" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AZ65" s="3"/>
+    </row>
+    <row r="66" customHeight="true" ht="18.0">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>26泸建01</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>283892.SH</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>24泸州城投PPN002</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>2.97Y</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>2.1108</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>泸州市城市建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>D+ 7.50</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>09-09 15:00</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>四川省-泸州市</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23泸建01,23泸建02]</t>
+        </is>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,华西证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr">
+        <is>
+          <t>泸州两江投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="AE66" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF66" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="inlineStr">
+        <is>
+          <t>泸州市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI66" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ66" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-10</t>
+        </is>
+      </c>
+      <c r="AK66" s="3"/>
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ66" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX66" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AZ66" s="3"/>
+    </row>
+    <row r="67" customHeight="true" ht="18.0">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>26环城01</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>283941.SH</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>24环城02</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>348D+2.00Y</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>1.8344</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>天津环城城市基础设施投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>C 27.24</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>09-09 15:00</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>天津市-西青区</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金3.40亿元拟用于全部用于偿还回售的公司债本金[23环城01]</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr">
+        <is>
+          <t>天津环城城市基础设施投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI67" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ67" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-10</t>
+        </is>
+      </c>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-10</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX67" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AZ67" s="3"/>
+    </row>
+    <row r="68" customHeight="true" ht="18.0">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>26建集Y5</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>246013.SH</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>24建集Y4</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>2.94Y+N</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>2.0250</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>厦门建发集团有限公司</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.52</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>09-09 16:00</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>福建省-厦门市</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟用于置换已用于偿还到期公司债券本金的自有资金。[23建集Y3,21建集01]</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,兴业证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD68" s="3"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr">
+        <is>
+          <t>厦门建发集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)(品种一)</t>
+        </is>
+      </c>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK68" s="3"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr">
+        <is>
+          <t>贸易零售</t>
+        </is>
+      </c>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX68" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AZ68" s="3"/>
+    </row>
+    <row r="69" customHeight="true" ht="18.0">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>26建集Y6</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>09-09 18:00</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>246014.SH</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>5+N</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>2.10 ~ 3.10</t>
+        </is>
+      </c>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>26建发集MTN003</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>4.92Y</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>2.1444</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>--/2.1100</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>厦门建发集团有限公司</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.52</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>09-09 16:00</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>福建省-厦门市</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟用于置换已用于偿还到期公司债券本金的自有资金。[23建集Y3,21建集01]</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,兴业证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD69" s="3"/>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr">
+        <is>
+          <t>厦门建发集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)(品种二)</t>
+        </is>
+      </c>
+      <c r="AI69" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ69" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK69" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL69" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ69" s="3" t="inlineStr">
+        <is>
+          <t>贸易零售</t>
+        </is>
+      </c>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX69" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AZ69" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
